--- a/artfynd/A 29817-2021 artfynd.xlsx
+++ b/artfynd/A 29817-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 29817-2021 artfynd.xlsx
+++ b/artfynd/A 29817-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2373,6 +2373,130 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>123512385</v>
+      </c>
+      <c r="B16" t="n">
+        <v>105443</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>340</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Ryl</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Chimaphila umbellata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Floraväktarlokalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>692269</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6582113</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Värmdö</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Gustavsberg</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På floraväktarlokalen</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anders Erixon</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anders Erixon, Marsha Thalin</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29817-2021 artfynd.xlsx
+++ b/artfynd/A 29817-2021 artfynd.xlsx
@@ -2378,7 +2378,7 @@
         <v>123512385</v>
       </c>
       <c r="B16" t="n">
-        <v>105443</v>
+        <v>105446</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/artfynd/A 29817-2021 artfynd.xlsx
+++ b/artfynd/A 29817-2021 artfynd.xlsx
@@ -2378,7 +2378,7 @@
         <v>123512385</v>
       </c>
       <c r="B16" t="n">
-        <v>105446</v>
+        <v>105463</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/artfynd/A 29817-2021 artfynd.xlsx
+++ b/artfynd/A 29817-2021 artfynd.xlsx
@@ -2378,7 +2378,7 @@
         <v>123512385</v>
       </c>
       <c r="B16" t="n">
-        <v>105463</v>
+        <v>105479</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anders Erixon, Marsha Thalin</t>
+          <t>Marsha Thalin, Anders Erixon</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>

--- a/artfynd/A 29817-2021 artfynd.xlsx
+++ b/artfynd/A 29817-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2245,10 +2245,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113409099</v>
+        <v>123512385</v>
       </c>
       <c r="B15" t="n">
-        <v>104698</v>
+        <v>105481</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2280,12 +2280,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2293,19 +2293,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mörkdalen V om, vid stigkors (*ryl* /stjälk/), Upl</t>
+          <t>Floraväktarlokalen, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>692259</v>
+        <v>692269</v>
       </c>
       <c r="R15" t="n">
-        <v>6582130</v>
+        <v>6582113</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2327,24 +2329,19 @@
           <t>Gustavsberg</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>AB-Vär-0370</t>
-        </is>
-      </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>W. Mörkdalen, Obskoord: 6581957/1646669/50 m (Avst fr FV-lokal: 180 m). Ö. Motions-banan, i slänten; 15 utvecklade skott. ( Återsedd.)</t>
+          <t>På floraväktarlokalen</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2353,149 +2350,22 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Anders Erixon</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Henry Gudmundson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>123512385</v>
-      </c>
-      <c r="B16" t="n">
-        <v>105479</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>EN</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>340</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Ryl</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Chimaphila umbellata</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(L.) W. P. C. Barton</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Floraväktarlokalen, Upl</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>692269</v>
-      </c>
-      <c r="R16" t="n">
-        <v>6582113</v>
-      </c>
-      <c r="S16" t="n">
-        <v>5</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Stockholm</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Värmdö</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Gustavsberg</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2025-03-26</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2025-03-26</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På floraväktarlokalen</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF16" t="inlineStr"/>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Anders Erixon</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Marsha Thalin, Anders Erixon</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+          <t>Anders Erixon, Marsha Thalin</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29817-2021 artfynd.xlsx
+++ b/artfynd/A 29817-2021 artfynd.xlsx
@@ -2248,7 +2248,7 @@
         <v>123512385</v>
       </c>
       <c r="B15" t="n">
-        <v>105481</v>
+        <v>105056</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 29817-2021 artfynd.xlsx
+++ b/artfynd/A 29817-2021 artfynd.xlsx
@@ -2362,7 +2362,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Erixon, Marsha Thalin</t>
+          <t>Marsha Thalin, Anders Erixon</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 29817-2021 artfynd.xlsx
+++ b/artfynd/A 29817-2021 artfynd.xlsx
@@ -2362,7 +2362,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Marsha Thalin, Anders Erixon</t>
+          <t>Anders Erixon, Marsha Thalin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
